--- a/output/pdf_financials_xlsx/HZ.xlsx
+++ b/output/pdf_financials_xlsx/HZ.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.281855</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.297505</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.362377</v>
       </c>
     </row>
     <row r="93">
@@ -2323,13 +2323,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.303729</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.710539</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.6103</v>
       </c>
     </row>
     <row r="119">
@@ -3146,7 +3146,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -3681,7 +3685,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>0.281855</v>
       </c>
@@ -4103,7 +4111,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
         <v>-0.303729</v>
       </c>

--- a/output/pdf_financials_xlsx/HZ.xlsx
+++ b/output/pdf_financials_xlsx/HZ.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.674897</v>
+        <v>1.261406</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.551562</v>
+        <v>2.042565</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.413122</v>
+        <v>0.705475</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.674897</v>
+        <v>-1.261406</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.551562</v>
+        <v>-2.042565</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.413122</v>
+        <v>-0.705475</v>
       </c>
     </row>
     <row r="12">
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.039589</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.016326</v>
       </c>
     </row>
     <row r="13">
@@ -864,10 +864,10 @@
         <v>-1.264828</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.680215</v>
+        <v>-2.719804</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.744178</v>
+        <v>-0.760504</v>
       </c>
     </row>
     <row r="28">
@@ -896,10 +896,10 @@
         <v>-1.264828</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.680215</v>
+        <v>-2.719804</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.744178</v>
+        <v>-0.760504</v>
       </c>
     </row>
     <row r="30">
@@ -5205,17 +5205,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>-1.261406</v>
+        <v>1.261406</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-2.042565</v>
+        <v>2.042565</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.705475</v>
+        <v>0.705475</v>
       </c>
     </row>
     <row r="85">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">

--- a/output/pdf_financials_xlsx/HZ.xlsx
+++ b/output/pdf_financials_xlsx/HZ.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.674897</v>
+        <v>0.736169</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.551562</v>
+        <v>0.603923</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.413122</v>
+        <v>0.452717</v>
       </c>
     </row>
     <row r="8">
@@ -4961,7 +4961,11 @@
           <t>Director fees 7</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -5023,7 +5027,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="n">
         <v>0.007605</v>
       </c>
@@ -6116,7 +6124,11 @@
           <t>Director fees 9</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E115" s="5" t="n">
         <v>0.053667</v>
       </c>
